--- a/reports/service-tracking-report-license_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
+++ b/reports/service-tracking-report-license_cache_ServiceTracking-XIV-202501-202612.xlsx.xlsx
@@ -126,7 +126,7 @@
     <x:numFmt numFmtId="165" formatCode="MMMM dd, yyyy"/>
     <x:numFmt numFmtId="166" formatCode="#,##0.00"/>
   </x:numFmts>
-  <x:fonts count="13">
+  <x:fonts count="12">
     <x:font>
       <x:sz val="10.0"/>
       <x:color rgb="FF000000"/>
@@ -166,14 +166,6 @@
       <x:sz val="13.0"/>
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Calibri"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:vertAlign val="baseline"/>
-      <x:sz val="12"/>
-      <x:color rgb="FF000000"/>
-      <x:name val="Calibri"/>
-      <x:family val="2"/>
     </x:font>
     <x:font>
       <x:b/>
@@ -446,7 +438,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="26">
+  <x:cellStyleXfs count="25">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
@@ -457,16 +449,13 @@
     <x:xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="7" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
@@ -478,53 +467,53 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="166" fontId="10" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="2" borderId="3" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="9" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="32">
+  <x:cellXfs count="31">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0" shrinkToFit="0" readingOrder="0"/>
     </x:xf>
@@ -559,87 +548,83 @@
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="166" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="166" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="165" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -941,17 +926,17 @@
       <x:c r="B5" s="12">
         <x:v>46113</x:v>
       </x:c>
-      <x:c r="C5" s="13" t="s"/>
-      <x:c r="D5" s="13" t="s"/>
-      <x:c r="E5" s="13" t="s"/>
-      <x:c r="F5" s="13" t="s"/>
-      <x:c r="G5" s="13" t="s"/>
-      <x:c r="H5" s="13" t="s"/>
-      <x:c r="I5" s="13" t="s"/>
-      <x:c r="J5" s="13" t="s"/>
-      <x:c r="K5" s="13" t="s"/>
-      <x:c r="L5" s="13" t="s"/>
-      <x:c r="M5" s="13" t="s"/>
+      <x:c r="C5" s="11" t="s"/>
+      <x:c r="D5" s="11" t="s"/>
+      <x:c r="E5" s="11" t="s"/>
+      <x:c r="F5" s="11" t="s"/>
+      <x:c r="G5" s="11" t="s"/>
+      <x:c r="H5" s="11" t="s"/>
+      <x:c r="I5" s="11" t="s"/>
+      <x:c r="J5" s="11" t="s"/>
+      <x:c r="K5" s="11" t="s"/>
+      <x:c r="L5" s="11" t="s"/>
+      <x:c r="M5" s="11" t="s"/>
       <x:c r="N5" s="4" t="s"/>
       <x:c r="O5" s="5" t="s"/>
       <x:c r="P5" s="5" t="s"/>
@@ -974,162 +959,162 @@
     </x:row>
     <x:row r="7" spans="1:28" ht="20" customHeight="1">
       <x:c r="A7" s="6" t="s"/>
-      <x:c r="B7" s="14" t="s">
+      <x:c r="B7" s="13" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C7" s="14" t="s">
+      <x:c r="C7" s="13" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D7" s="14" t="s">
+      <x:c r="D7" s="13" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E7" s="14" t="s">
+      <x:c r="E7" s="13" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="F7" s="14" t="s">
+      <x:c r="F7" s="13" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="G7" s="14" t="s">
+      <x:c r="G7" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="14" t="s">
+      <x:c r="H7" s="13" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="I7" s="14" t="s">
+      <x:c r="I7" s="13" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J7" s="14" t="s">
+      <x:c r="J7" s="13" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K7" s="14" t="s">
+      <x:c r="K7" s="13" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="L7" s="14" t="s">
+      <x:c r="L7" s="13" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="M7" s="14" t="s">
+      <x:c r="M7" s="13" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="N7" s="6" t="s"/>
     </x:row>
     <x:row r="8" spans="1:28" ht="30" customHeight="1">
       <x:c r="A8" s="6" t="s"/>
-      <x:c r="B8" s="15" t="s">
+      <x:c r="B8" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C8" s="15" t="s">
+      <x:c r="C8" s="14" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="D8" s="16" t="s">
+      <x:c r="D8" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E8" s="15" t="s">
+      <x:c r="E8" s="14" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="F8" s="15" t="s">
+      <x:c r="F8" s="14" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="G8" s="15" t="s">
+      <x:c r="G8" s="14" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="H8" s="17">
+      <x:c r="H8" s="16">
         <x:v>46124.1607868981</x:v>
       </x:c>
-      <x:c r="I8" s="17">
+      <x:c r="I8" s="16">
         <x:v>46023</x:v>
       </x:c>
-      <x:c r="J8" s="16" t="s">
+      <x:c r="J8" s="15" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="K8" s="18" t="n">
+      <x:c r="K8" s="17" t="n">
         <x:v>3100</x:v>
       </x:c>
-      <x:c r="L8" s="19">
+      <x:c r="L8" s="18">
         <x:v>46124.1624131829</x:v>
       </x:c>
-      <x:c r="M8" s="15" t="s">
+      <x:c r="M8" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B9" s="15" t="s">
+      <x:c r="B9" s="14" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C9" s="15" t="s">
+      <x:c r="C9" s="14" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="D9" s="16" t="s">
+      <x:c r="D9" s="15" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="E9" s="15" t="s">
+      <x:c r="E9" s="14" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="F9" s="15" t="s">
+      <x:c r="F9" s="14" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="G9" s="15" t="s">
+      <x:c r="G9" s="14" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="H9" s="17">
+      <x:c r="H9" s="16">
         <x:v>46125.0306295139</x:v>
       </x:c>
-      <x:c r="I9" s="17">
+      <x:c r="I9" s="16">
         <x:v>46215</x:v>
       </x:c>
-      <x:c r="J9" s="16" t="s">
+      <x:c r="J9" s="15" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="K9" s="18" t="n">
+      <x:c r="K9" s="17" t="n">
         <x:v>3006</x:v>
       </x:c>
-      <x:c r="L9" s="19">
+      <x:c r="L9" s="18">
         <x:v>46125.0821987731</x:v>
       </x:c>
-      <x:c r="M9" s="15" t="s">
+      <x:c r="M9" s="14" t="s">
         <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="11" spans="1:28" ht="15.75" customHeight="1"/>
     <x:row r="12" spans="1:28" ht="30" customHeight="1">
-      <x:c r="B12" s="20" t="s">
+      <x:c r="B12" s="19" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="C12" s="21" t="s"/>
-      <x:c r="D12" s="21" t="s"/>
-      <x:c r="E12" s="22" t="s"/>
-      <x:c r="F12" s="22" t="s"/>
+      <x:c r="C12" s="20" t="s"/>
+      <x:c r="D12" s="20" t="s"/>
+      <x:c r="E12" s="21" t="s"/>
+      <x:c r="F12" s="21" t="s"/>
     </x:row>
     <x:row r="13" spans="1:28" ht="22" customHeight="1">
-      <x:c r="B13" s="23" t="s">
+      <x:c r="B13" s="22" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="C13" s="24" t="s"/>
-      <x:c r="D13" s="24" t="s"/>
-      <x:c r="E13" s="24" t="s"/>
-      <x:c r="F13" s="25" t="s">
+      <x:c r="C13" s="23" t="s"/>
+      <x:c r="D13" s="23" t="s"/>
+      <x:c r="E13" s="23" t="s"/>
+      <x:c r="F13" s="24" t="s">
         <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:28" ht="18" customHeight="1">
-      <x:c r="B14" s="26" t="s">
+      <x:c r="B14" s="25" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C14" s="27" t="s"/>
-      <x:c r="D14" s="27" t="s"/>
-      <x:c r="E14" s="27" t="s"/>
-      <x:c r="F14" s="28" t="n">
+      <x:c r="C14" s="26" t="s"/>
+      <x:c r="D14" s="26" t="s"/>
+      <x:c r="E14" s="26" t="s"/>
+      <x:c r="F14" s="27" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:28" ht="28" customHeight="1">
-      <x:c r="B15" s="29" t="s">
+      <x:c r="B15" s="28" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="C15" s="30" t="s"/>
-      <x:c r="D15" s="30" t="s"/>
-      <x:c r="E15" s="30" t="s"/>
-      <x:c r="F15" s="31" t="n">
+      <x:c r="C15" s="29" t="s"/>
+      <x:c r="D15" s="29" t="s"/>
+      <x:c r="E15" s="29" t="s"/>
+      <x:c r="F15" s="30" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
